--- a/api/clv1/codelist/Country.xlsx
+++ b/api/clv1/codelist/Country.xlsx
@@ -1351,7 +1351,7 @@
     <t>SY</t>
   </si>
   <si>
-    <t>Syrian Arab Republic</t>
+    <t>Syrian Arab Republic (the)</t>
   </si>
   <si>
     <t>TW</t>
@@ -1369,7 +1369,7 @@
     <t>TZ</t>
   </si>
   <si>
-    <t>Tanzania, United Republic of</t>
+    <t>Tanzania, the United Republic of</t>
   </si>
   <si>
     <t>TH</t>

--- a/api/clv1/codelist/Country.xlsx
+++ b/api/clv1/codelist/Country.xlsx
@@ -991,7 +991,7 @@
     <t>AN</t>
   </si>
   <si>
-    <t>NETHERLAND ANTILLES</t>
+    <t>Netherlands Antilles</t>
   </si>
   <si>
     <t>NC</t>

--- a/api/clv1/codelist/Country.xlsx
+++ b/api/clv1/codelist/Country.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="522">
   <si>
     <t>code</t>
   </si>
@@ -256,6 +256,12 @@
     <t>Burkina Faso</t>
   </si>
   <si>
+    <t>BU</t>
+  </si>
+  <si>
+    <t>Burma</t>
+  </si>
+  <si>
     <t>BI</t>
   </si>
   <si>
@@ -424,6 +430,12 @@
     <t>Dominican Republic (the)</t>
   </si>
   <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>East Timor</t>
+  </si>
+  <si>
     <t>EC</t>
   </si>
   <si>
@@ -994,6 +1006,12 @@
     <t>Netherlands Antilles</t>
   </si>
   <si>
+    <t>NT</t>
+  </si>
+  <si>
+    <t>Neutral Zone</t>
+  </si>
+  <si>
     <t>NC</t>
   </si>
   <si>
@@ -1336,6 +1354,12 @@
     <t>Eswatini</t>
   </si>
   <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>Serbia and Montenegro</t>
+  </si>
+  <si>
     <t>SE</t>
   </si>
   <si>
@@ -1532,6 +1556,18 @@
   </si>
   <si>
     <t>Yemen</t>
+  </si>
+  <si>
+    <t>YU</t>
+  </si>
+  <si>
+    <t>Yugoslavia</t>
+  </si>
+  <si>
+    <t>ZR</t>
+  </si>
+  <si>
+    <t>Zaire</t>
   </si>
   <si>
     <t>ZM</t>
@@ -1875,7 +1911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G252"/>
+  <dimension ref="A1:G258"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -4662,6 +4698,72 @@
         <v>9</v>
       </c>
     </row>
+    <row r="253" spans="1:4">
+      <c r="A253" t="s">
+        <v>510</v>
+      </c>
+      <c r="B253" t="s">
+        <v>511</v>
+      </c>
+      <c r="D253" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" t="s">
+        <v>512</v>
+      </c>
+      <c r="B254" t="s">
+        <v>513</v>
+      </c>
+      <c r="D254" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" t="s">
+        <v>514</v>
+      </c>
+      <c r="B255" t="s">
+        <v>515</v>
+      </c>
+      <c r="D255" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" t="s">
+        <v>516</v>
+      </c>
+      <c r="B256" t="s">
+        <v>517</v>
+      </c>
+      <c r="D256" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" t="s">
+        <v>518</v>
+      </c>
+      <c r="B257" t="s">
+        <v>519</v>
+      </c>
+      <c r="D257" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" t="s">
+        <v>520</v>
+      </c>
+      <c r="B258" t="s">
+        <v>521</v>
+      </c>
+      <c r="D258" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
